--- a/outputs/38703.xlsx
+++ b/outputs/38703.xlsx
@@ -254,44 +254,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -547,578 +551,578 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B2" s="2" t="n">
+    <row r="2" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>0.412638888888889</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B3" s="2" t="n">
+      <c r="G2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>0.413634259259259</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B4" s="2" t="n">
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>0.41525462962963</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B5" s="2" t="n">
+      <c r="G4" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>0.417106481481482</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B6" s="2" t="n">
+      <c r="G5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>0.418518518518519</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B7" s="2" t="n">
+      <c r="G6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>0.42087962962963</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B8" s="2" t="n">
+      <c r="F7" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B8" s="3" t="n">
         <v>0.425625</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B9" s="2" t="n">
+      <c r="G8" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B9" s="3" t="n">
         <v>0.429571759259259</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B10" s="2" t="n">
+      <c r="G9" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B10" s="3" t="n">
         <v>0.436493055555556</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="3" t="n">
+      <c r="G10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="4" t="n">
         <f aca="false">SUMPRODUCT(1/COUNTIF(E2:E10,E2:E10))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="11" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B11" s="6" t="n">
+    <row r="11" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B11" s="7" t="n">
         <v>0.4878125</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="8" t="n">
         <v>-15</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B12" s="6" t="n">
+      <c r="G11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B12" s="7" t="n">
         <v>0.488113425925926</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="8" t="n">
         <v>-1</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B13" s="6" t="n">
+      <c r="G12" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B13" s="7" t="n">
         <v>0.488391203703704</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="8" t="n">
         <v>-2</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B14" s="6" t="n">
+      <c r="G13" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B14" s="7" t="n">
         <v>0.488622685185185</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="8" t="n">
         <v>-3</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B15" s="6" t="n">
+      <c r="G14" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B15" s="7" t="n">
         <v>0.489444444444445</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="8" t="n">
         <v>-40</v>
       </c>
-      <c r="G15" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B16" s="6" t="n">
+      <c r="G15" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B16" s="7" t="n">
         <v>0.489814814814815</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="8" t="n">
         <v>-2</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B17" s="6" t="n">
+      <c r="G16" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B17" s="7" t="n">
         <v>0.490185185185185</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="8" t="n">
         <v>-5</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B18" s="6" t="n">
+      <c r="G17" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B18" s="7" t="n">
         <v>0.490555555555556</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="8" t="n">
         <v>-8</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B19" s="6" t="n">
+      <c r="G18" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B19" s="7" t="n">
         <v>0.49119212962963</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="8" t="n">
         <v>-5</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B20" s="6" t="n">
+      <c r="G19" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B20" s="7" t="n">
         <v>0.491689814814815</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="8" t="n">
         <v>-10</v>
       </c>
-      <c r="G20" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H20" s="7" t="n">
+      <c r="G20" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="8" t="n">
         <f aca="false">SUMPRODUCT(1/COUNTIF(E11:E20,E11:E20))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="21" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B21" s="2" t="n">
+    <row r="21" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B21" s="3" t="n">
         <v>0.585706018518519</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="C21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G21" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B22" s="2" t="n">
+      <c r="G21" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B22" s="3" t="n">
         <v>0.607881944444444</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="C22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B23" s="2" t="n">
+      <c r="G22" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B23" s="3" t="n">
         <v>0.61818287037037</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G23" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>44950</v>
-      </c>
-      <c r="B24" s="2" t="n">
+      <c r="G23" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="n">
+        <v>44950</v>
+      </c>
+      <c r="B24" s="3" t="n">
         <v>0.619016203703704</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="C24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G24" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H24" s="3" t="n">
+      <c r="G24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="4" t="n">
         <f aca="false">SUMPRODUCT(1/COUNTIF(E21:E24,E21:E24))</f>
         <v>4</v>
       </c>

--- a/outputs/38703.xlsx
+++ b/outputs/38703.xlsx
@@ -605,7 +605,10 @@
       <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="5"/>
+      <c r="H2" s="5" t="n">
+        <f aca="false">SUMPRODUCT(1/COUNTIF($E$2:$E$10,E2:E10))</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="3" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
@@ -790,10 +793,6 @@
       <c r="G10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="4" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF(E2:E10,E2:E10))</f>
-        <v>9</v>
-      </c>
     </row>
     <row r="11" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
@@ -1026,7 +1025,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="8" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF(E11:E20,E11:E20))</f>
+        <f aca="false">SUMPRODUCT(1/COUNTIF($E$11:$E$20,E11:E20))</f>
         <v>9</v>
       </c>
     </row>
@@ -1123,7 +1122,7 @@
         <v>10</v>
       </c>
       <c r="H24" s="4" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF(E21:E24,E21:E24))</f>
+        <f aca="false">SUMPRODUCT(1/COUNTIF($E$21:$E$24,E21:E24))</f>
         <v>4</v>
       </c>
     </row>
